--- a/TestData2.xlsx
+++ b/TestData2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\viral\EUC Insight\886 SP1 SC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urjita\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3939651C-5C18-4AE6-9F29-B1B0212B9091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A94C7C6-70C3-40F5-A218-D3DC1FEE31BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4A17209D-F533-42A2-BC03-DB7072C262BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A17209D-F533-42A2-BC03-DB7072C262BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -97,9 +97,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +137,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -243,7 +243,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -385,7 +385,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -817,9 +817,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
+      <c r="L13" s="1"/>
       <c r="M13" s="1">
         <v>11</v>
       </c>
@@ -863,9 +861,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1">
-        <v>2</v>
-      </c>
+      <c r="L14" s="1"/>
       <c r="M14" s="1">
         <v>12</v>
       </c>
@@ -909,9 +905,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1">
-        <v>3</v>
-      </c>
+      <c r="L15" s="1"/>
       <c r="M15" s="1">
         <v>13</v>
       </c>
@@ -952,9 +946,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1">
-        <v>4</v>
-      </c>
+      <c r="L16" s="1"/>
       <c r="M16" s="1">
         <v>14</v>
       </c>
@@ -995,9 +987,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1">
-        <v>5</v>
-      </c>
+      <c r="L17" s="1"/>
       <c r="M17" s="1">
         <v>15</v>
       </c>
@@ -1038,9 +1028,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1">
-        <v>6</v>
-      </c>
+      <c r="L18" s="1"/>
       <c r="M18" s="1">
         <v>16</v>
       </c>
@@ -1081,9 +1069,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1">
-        <v>7</v>
-      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1">
         <v>17</v>
       </c>
@@ -1124,9 +1110,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1">
-        <v>8</v>
-      </c>
+      <c r="L20" s="1"/>
       <c r="M20" s="1">
         <v>18</v>
       </c>
@@ -1167,9 +1151,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1">
-        <v>9</v>
-      </c>
+      <c r="L21" s="1"/>
       <c r="M21" s="1">
         <v>19</v>
       </c>
@@ -1210,9 +1192,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1">
-        <v>10</v>
-      </c>
+      <c r="L22" s="1"/>
       <c r="M22" s="1">
         <v>20</v>
       </c>
